--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -3775,7 +3775,7 @@
         <v>136603751</v>
       </c>
       <c r="B32" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>136603747</v>
       </c>
       <c r="B68" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>136603752</v>
       </c>
       <c r="B69" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>136603744</v>
       </c>
       <c r="B82" t="n">
-        <v>93438</v>
+        <v>93441</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -3775,7 +3775,7 @@
         <v>136603751</v>
       </c>
       <c r="B32" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>136603747</v>
       </c>
       <c r="B68" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>136603752</v>
       </c>
       <c r="B69" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>136603744</v>
       </c>
       <c r="B82" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -3775,7 +3775,7 @@
         <v>136603751</v>
       </c>
       <c r="B32" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>136603747</v>
       </c>
       <c r="B68" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>136603752</v>
       </c>
       <c r="B69" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>136603744</v>
       </c>
       <c r="B82" t="n">
-        <v>93442</v>
+        <v>93447</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>136603753</v>
       </c>
       <c r="B89" t="n">
-        <v>79497</v>
+        <v>79499</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -3775,7 +3775,7 @@
         <v>136603751</v>
       </c>
       <c r="B32" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>136603747</v>
       </c>
       <c r="B68" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>136603752</v>
       </c>
       <c r="B69" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>136603744</v>
       </c>
       <c r="B82" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -3775,7 +3775,7 @@
         <v>136603751</v>
       </c>
       <c r="B32" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>136603747</v>
       </c>
       <c r="B68" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>136603752</v>
       </c>
       <c r="B69" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>136603744</v>
       </c>
       <c r="B82" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>136603753</v>
       </c>
       <c r="B89" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -3775,7 +3775,7 @@
         <v>136603751</v>
       </c>
       <c r="B32" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>136603747</v>
       </c>
       <c r="B68" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>136603752</v>
       </c>
       <c r="B69" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>136603744</v>
       </c>
       <c r="B82" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>136603753</v>
       </c>
       <c r="B89" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -3775,7 +3775,7 @@
         <v>136603751</v>
       </c>
       <c r="B32" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>136603747</v>
       </c>
       <c r="B68" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>136603752</v>
       </c>
       <c r="B69" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>136603744</v>
       </c>
       <c r="B82" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>136603753</v>
       </c>
       <c r="B89" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -3775,7 +3775,7 @@
         <v>136603751</v>
       </c>
       <c r="B32" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>136603747</v>
       </c>
       <c r="B68" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>136603752</v>
       </c>
       <c r="B69" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>136603744</v>
       </c>
       <c r="B82" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -3775,7 +3775,7 @@
         <v>136603751</v>
       </c>
       <c r="B32" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>136603747</v>
       </c>
       <c r="B68" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>136603752</v>
       </c>
       <c r="B69" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>136603744</v>
       </c>
       <c r="B82" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>136603753</v>
       </c>
       <c r="B89" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -3775,7 +3775,7 @@
         <v>136603751</v>
       </c>
       <c r="B32" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>136603747</v>
       </c>
       <c r="B68" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>136603752</v>
       </c>
       <c r="B69" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>136603744</v>
       </c>
       <c r="B82" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>136603753</v>
       </c>
       <c r="B89" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 18726-2024 artfynd.xlsx
+++ b/artfynd/A 18726-2024 artfynd.xlsx
@@ -3775,7 +3775,7 @@
         <v>136603751</v>
       </c>
       <c r="B32" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7493,7 +7493,7 @@
         <v>136603747</v>
       </c>
       <c r="B68" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7605,7 +7605,7 @@
         <v>136603752</v>
       </c>
       <c r="B69" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         <v>136603744</v>
       </c>
       <c r="B82" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9686,7 +9686,7 @@
         <v>136603753</v>
       </c>
       <c r="B89" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
